--- a/语文群_20260901.xlsx
+++ b/语文群_20260901.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luhui\Python\checkin_v2\WeChatTextExport\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_FE6A3523B048951AFB34376E611550E1EF58E689" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_FE6A3523991580291734371431517BFBEF58E6C2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16890" yWindow="50" windowWidth="19720" windowHeight="20950" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,12 +33,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>学号</t>
   </si>
   <si>
     <t>累计打卡天数</t>
+  </si>
+  <si>
+    <t>当天语文打卡</t>
+  </si>
+  <si>
+    <t>过往打卡天数</t>
   </si>
 </sst>
 </file>
@@ -431,11 +437,11 @@
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="3">
-        <v>0</v>
-      </c>
-      <c r="D2" s="3">
-        <v>0</v>
+      <c r="C2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
